--- a/test_data/icpms_test/Test_Data_Results_2025_03_31.xlsx
+++ b/test_data/icpms_test/Test_Data_Results_2025_03_31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Daven/Projects/Sparrow/Labs/Sparrow-CU-TRaIL/test_data/icpms_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1573D47-E9CA-2748-8891-04414BD88B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E723DDD1-57C5-AF4B-8E06-E1C25F0E5903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="760" windowWidth="25880" windowHeight="21580" xr2:uid="{AB9FA966-99FF-A742-8C7A-DCACFBC5B889}"/>
   </bookViews>
